--- a/artfynd/A 12247-2026 artfynd.xlsx
+++ b/artfynd/A 12247-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132225122</v>
+        <v>132225350</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Labbenäs, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540016</v>
+        <v>540010</v>
       </c>
       <c r="R2" t="n">
-        <v>6463483</v>
+        <v>6463455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132225481</v>
+        <v>132225122</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -823,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540010</v>
+        <v>540016</v>
       </c>
       <c r="R3" t="n">
-        <v>6463455</v>
+        <v>6463483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,35 +877,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132225350</v>
+        <v>132225481</v>
       </c>
       <c r="B4" t="n">
-        <v>97370</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Labbenäs, Ög</t>
@@ -979,6 +979,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110361159</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövskogar NV Sjösätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>540040</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6463380</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vist</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12247-2026 artfynd.xlsx
+++ b/artfynd/A 12247-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132225350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132225122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132225481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>